--- a/data/vocabulary.xlsx
+++ b/data/vocabulary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="20"/>
+    <workbookView activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet state="visible" name="Family" sheetId="1" r:id="rId4"/>
@@ -17703,6 +17703,12 @@
   </si>
   <si>
     <t>피자를 먹을지 초밥을 먹을지는 당신 마음에 달렸어요.</t>
+  </si>
+  <si>
+    <t>padre soltero o madre soltera</t>
+  </si>
+  <si>
+    <t>Ser padre soltero o madre soltera es un trabajo difícil pero gratificante.</t>
   </si>
 </sst>
 </file>
@@ -18562,7 +18568,7 @@
         <v>84</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>85</v>
+        <v>5887</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>86</v>
@@ -18582,7 +18588,7 @@
         <v>88</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>89</v>
+        <v>5888</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>

--- a/data/vocabulary.xlsx
+++ b/data/vocabulary.xlsx
@@ -3,34 +3,34 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="7"/>
+    <workbookView activeTab="9"/>
   </bookViews>
   <sheets>
-    <sheet state="visible" name="Family" sheetId="1" r:id="rId4"/>
+    <sheet name="Greetings, Basics &amp; Courtesy" sheetId="21" r:id="rId25"/>
+    <sheet name="Questions, Directions &amp; Emergen" sheetId="22" r:id="rId26"/>
+    <sheet name="Daily Life, Routine &amp; Feelings" sheetId="23" r:id="rId27"/>
+    <sheet name="Restaurant, Food &amp; Shopping" sheetId="24" r:id="rId28"/>
+    <sheet name="Travel, Lodging &amp; Weather" sheetId="25" r:id="rId29"/>
+    <sheet state="visible" name="Emotions" sheetId="19" r:id="rId22"/>
     <sheet state="visible" name="House and Home" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Weather" sheetId="9" r:id="rId12"/>
     <sheet state="visible" name="Shopping" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Daily Routine" sheetId="10" r:id="rId13"/>
     <sheet state="visible" name="At the Doctor" sheetId="4" r:id="rId7"/>
     <sheet state="visible" name="Food and Drinks" sheetId="5" r:id="rId8"/>
     <sheet state="visible" name="Work" sheetId="6" r:id="rId9"/>
     <sheet state="visible" name="School" sheetId="7" r:id="rId10"/>
     <sheet state="visible" name="Travel" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="Weather" sheetId="9" r:id="rId12"/>
-    <sheet state="visible" name="Daily Routine" sheetId="10" r:id="rId13"/>
     <sheet state="visible" name="Hobbies" sheetId="11" r:id="rId14"/>
     <sheet state="visible" name="Clothes" sheetId="12" r:id="rId15"/>
     <sheet state="visible" name="Transport" sheetId="13" r:id="rId16"/>
     <sheet state="visible" name="Restaurant" sheetId="14" r:id="rId17"/>
     <sheet state="visible" name="Friends and Relationships" sheetId="15" r:id="rId18"/>
+    <sheet state="visible" name="Family" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Technology" sheetId="16" r:id="rId19"/>
     <sheet state="visible" name="Holidays" sheetId="17" r:id="rId20"/>
     <sheet state="visible" name="Sports" sheetId="18" r:id="rId21"/>
-    <sheet state="visible" name="Emotions" sheetId="19" r:id="rId22"/>
     <sheet state="visible" name="City and Directions" sheetId="20" r:id="rId23"/>
-    <sheet name="Greetings, Basics &amp; Courtesy" sheetId="21" r:id="rId25"/>
-    <sheet name="Questions, Directions &amp; Emergen" sheetId="22" r:id="rId26"/>
-    <sheet name="Daily Life, Routine &amp; Feelings" sheetId="23" r:id="rId27"/>
-    <sheet name="Restaurant, Food &amp; Shopping" sheetId="24" r:id="rId28"/>
-    <sheet name="Travel, Lodging &amp; Weather" sheetId="25" r:id="rId29"/>
   </sheets>
   <calcPr calcId="171027"/>
   <extLst>
